--- a/scripts/python/backlog-xlsx/エビデンステンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/エビデンステンプレート.xlsx
@@ -1045,85 +1045,85 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1" s="10">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
+      <c r="A3" s="7" t="n"/>
+      <c r="B3" s="7" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="7" t="n"/>
     </row>
     <row r="4" ht="45" customHeight="1" s="10">
-      <c r="A4" s="4" t="n"/>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
+      <c r="A4" s="7" t="n"/>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1" s="10">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
+      <c r="A5" s="7" t="n"/>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
     </row>
     <row r="6" ht="60" customHeight="1" s="10">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
+      <c r="A6" s="7" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
     </row>
     <row r="7" ht="60" customHeight="1" s="10">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
     </row>
     <row r="8" ht="60" customHeight="1" s="10">
-      <c r="A8" s="4" t="n"/>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
     </row>
     <row r="9" ht="45" customHeight="1" s="10">
-      <c r="A9" s="2" t="n"/>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
     </row>
     <row r="10" ht="45" customHeight="1" s="10">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
     </row>
     <row r="11" ht="45" customHeight="1" s="10">
-      <c r="A11" s="2" t="n"/>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1425,19 +1425,19 @@
       <c r="C9" s="8" t="n"/>
       <c r="D9" s="7" t="n"/>
     </row>
-    <row r="10" ht="25" customHeight="1" s="10">
+    <row r="10" s="10">
       <c r="A10" s="6" t="n"/>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="8" t="n"/>
       <c r="D10" s="7" t="n"/>
     </row>
-    <row r="11" ht="25" customHeight="1" s="10">
+    <row r="11" s="10">
       <c r="A11" s="6" t="n"/>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="8" t="n"/>
       <c r="D11" s="7" t="n"/>
     </row>
-    <row r="12" ht="25" customHeight="1" s="10">
+    <row r="12" s="10">
       <c r="A12" s="6" t="n"/>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="8" t="n"/>

--- a/scripts/python/backlog-xlsx/エビデンステンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/エビデンステンプレート.xlsx
@@ -361,344 +361,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>1</colOff>
-      <row>10</row>
-      <rowOff>1</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>976825</colOff>
-      <row>20</row>
-      <rowOff>6351</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="図 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1" y="3276601"/>
-          <a:ext cx="5726624" cy="3816350"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>1</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>546239</colOff>
-      <row>31</row>
-      <rowOff>336551</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="図 2"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="7505701"/>
-          <a:ext cx="5296039" cy="3765550"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>1</colOff>
-      <row>31</row>
-      <rowOff>342901</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>514351</colOff>
-      <row>53</row>
-      <rowOff>97498</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="図 3"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1" y="11277601"/>
-          <a:ext cx="5264150" cy="3539197"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>15</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>2766942</colOff>
-      <row>23</row>
-      <rowOff>120650</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="図 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="4673600"/>
-          <a:ext cx="7516742" cy="3168650"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>27</row>
-      <rowOff>1</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>2743200</colOff>
-      <row>31</row>
-      <rowOff>155991</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="図 2"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="8902701"/>
-          <a:ext cx="7493000" cy="1679990"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>31</row>
-      <rowOff>152400</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>2736850</colOff>
-      <row>34</row>
-      <rowOff>190222</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="図 3"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="10579100"/>
-          <a:ext cx="7486650" cy="1180822"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>34</row>
-      <rowOff>184150</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>3321050</colOff>
-      <row>36</row>
-      <rowOff>354219</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="図 4"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="11753850"/>
-          <a:ext cx="3740150" cy="932069"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>4</col>
-      <colOff>97710</colOff>
-      <row>26</row>
-      <rowOff>31751</rowOff>
-    </from>
-    <to>
-      <col>13</col>
-      <colOff>367882</colOff>
-      <row>36</row>
-      <rowOff>234950</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="図 6"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="7641510" y="8616951"/>
-          <a:ext cx="5756572" cy="3949699"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>

--- a/scripts/python/backlog-xlsx/エビデンステンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/エビデンステンプレート.xlsx
@@ -821,7 +821,7 @@
     <row r="2" ht="45" customHeight="1" s="10">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>テスト仕様シートの「実装前」「両方」の項目を実施し、エビデンスを貼り付けてください。</t>
+          <t>テスト仕様シートの「実装前」の項目を実施し、エビデンスを貼り付けてください。</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,6 @@
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1029,7 +1028,7 @@
     <row r="2" ht="30" customHeight="1" s="10">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>テスト仕様シートの「実装後」「両方」の項目を実施し、エビデンスを貼り付けてください。</t>
+          <t>テスト仕様シートの「実装後」の項目を実施し、エビデンスを貼り付けてください。</t>
         </is>
       </c>
     </row>
@@ -1354,6 +1353,5 @@
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>